--- a/experiments/nrp_sat_seq_exp_results.xlsx
+++ b/experiments/nrp_sat_seq_exp_results.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,30 +447,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -495,19 +485,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0212155</v>
+        <v>0.0267482</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00553272</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0267482</v>
-      </c>
-      <c r="I2" t="n">
         <v>14.1</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -528,19 +512,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0227718</v>
+        <v>0.0283921</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00562025</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0283921</v>
-      </c>
-      <c r="I3" t="n">
         <v>13.6</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,19 +539,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0206139</v>
+        <v>0.0253518</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00473788</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0253518</v>
-      </c>
-      <c r="I4" t="n">
         <v>14.2</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -594,19 +566,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0210196</v>
+        <v>0.0258845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00486491</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0258845</v>
-      </c>
-      <c r="I5" t="n">
         <v>14</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -627,19 +593,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0208091</v>
+        <v>0.0256042</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00479512</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0256042</v>
-      </c>
-      <c r="I6" t="n">
         <v>13.9</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -660,19 +620,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.021666</v>
+        <v>0.0278267</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00616065</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0278267</v>
-      </c>
-      <c r="I7" t="n">
         <v>14</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -693,19 +647,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0213643</v>
+        <v>0.0267478</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00538354</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0267478</v>
-      </c>
-      <c r="I8" t="n">
         <v>14</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -726,19 +674,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0211277</v>
+        <v>0.0264911</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00536333</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0264911</v>
-      </c>
-      <c r="I9" t="n">
         <v>13.9</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -759,19 +701,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0213639</v>
+        <v>0.0269279</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00556403</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0269279</v>
-      </c>
-      <c r="I10" t="n">
         <v>13.9</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -792,19 +728,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0225553</v>
+        <v>0.0289478</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00639248</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0289478</v>
-      </c>
-      <c r="I11" t="n">
         <v>13.6</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -827,19 +757,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02145071</v>
+        <v>0.02689221000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005441491</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.02689221000000001</v>
-      </c>
-      <c r="I12" t="n">
         <v>13.92</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -852,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,30 +807,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -931,19 +845,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0409223</v>
+        <v>0.051113</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0101907</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.051113</v>
-      </c>
-      <c r="I2" t="n">
         <v>26.6</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -964,19 +872,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0405839</v>
+        <v>0.0512624</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0106785</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0512624</v>
-      </c>
-      <c r="I3" t="n">
         <v>26.2</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,19 +899,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0428405</v>
+        <v>0.0534074</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0105669</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.0534074</v>
-      </c>
-      <c r="I4" t="n">
         <v>26.3</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1030,19 +926,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0503368</v>
+        <v>0.0619961</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0116593</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0619961</v>
-      </c>
-      <c r="I5" t="n">
         <v>26.8</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1063,19 +953,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0395168</v>
+        <v>0.0487845</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00926767</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0487845</v>
-      </c>
-      <c r="I6" t="n">
         <v>25.1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1096,19 +980,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0382896</v>
+        <v>0.046858</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00856849</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.046858</v>
-      </c>
-      <c r="I7" t="n">
         <v>25.9</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1129,19 +1007,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0440698</v>
+        <v>0.0555327</v>
       </c>
       <c r="G8" t="n">
-        <v>0.011463</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0555327</v>
-      </c>
-      <c r="I8" t="n">
         <v>26.1</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1162,19 +1034,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0434486</v>
+        <v>0.0545927</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0111441</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0545927</v>
-      </c>
-      <c r="I9" t="n">
         <v>26</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1195,19 +1061,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0398996</v>
+        <v>0.0504467</v>
       </c>
       <c r="G10" t="n">
-        <v>0.010547</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.0504467</v>
-      </c>
-      <c r="I10" t="n">
         <v>25.4</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1228,19 +1088,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0417122</v>
+        <v>0.0526908</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0109787</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0526908</v>
-      </c>
-      <c r="I11" t="n">
         <v>25.9</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1263,19 +1117,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04216200999999999</v>
+        <v>0.05266843</v>
       </c>
       <c r="G12" t="n">
-        <v>0.010506436</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.05266843</v>
-      </c>
-      <c r="I12" t="n">
         <v>26.03</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1288,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,30 +1167,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1367,19 +1205,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0673102</v>
+        <v>0.0827016</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0153914</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.0827016</v>
-      </c>
-      <c r="I2" t="n">
         <v>39.8</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1400,19 +1232,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0660911</v>
+        <v>0.0813265</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0152354</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.0813265</v>
-      </c>
-      <c r="I3" t="n">
         <v>40.1</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1433,19 +1259,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0713197</v>
+        <v>0.087113</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0157933</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.087113</v>
-      </c>
-      <c r="I4" t="n">
         <v>40.2</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1466,19 +1286,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0698058</v>
+        <v>0.0855417</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0157359</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0855417</v>
-      </c>
-      <c r="I5" t="n">
         <v>40</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1499,19 +1313,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07067320000000001</v>
+        <v>0.0872798</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0166065</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.0872798</v>
-      </c>
-      <c r="I6" t="n">
         <v>39.7</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1532,19 +1340,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0692395</v>
+        <v>0.0851399</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0159004</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.0851399</v>
-      </c>
-      <c r="I7" t="n">
         <v>40.5</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1565,19 +1367,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0738304</v>
+        <v>0.0900748</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0162444</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.0900748</v>
-      </c>
-      <c r="I8" t="n">
         <v>40.6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,19 +1394,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.07377590000000001</v>
+        <v>0.08965670000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0158808</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.08965670000000001</v>
-      </c>
-      <c r="I9" t="n">
         <v>40.8</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1631,19 +1421,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0699207</v>
+        <v>0.08599279999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0160721</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.08599279999999999</v>
-      </c>
-      <c r="I10" t="n">
         <v>39.8</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,19 +1448,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.06881089999999999</v>
+        <v>0.0834085</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0145976</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.0834085</v>
-      </c>
-      <c r="I11" t="n">
         <v>40.1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1699,19 +1477,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07007774000000001</v>
+        <v>0.08582353</v>
       </c>
       <c r="G12" t="n">
-        <v>0.01574578</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.08582353</v>
-      </c>
-      <c r="I12" t="n">
         <v>40.16000000000001</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1724,7 +1496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1755,30 +1527,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>encoding_time_sec</t>
+          <t>total_time_sec</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>solving_time_sec</t>
+          <t>peak_memory_mb</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_time_sec</t>
+          <t>total_clauses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>peak_memory_mb</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>total_clauses</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
         <is>
           <t>total_variables</t>
         </is>
@@ -1803,19 +1565,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0864198</v>
+        <v>0.106763</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0203437</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.106763</v>
-      </c>
-      <c r="I2" t="n">
         <v>46.9</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1836,19 +1592,13 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0847165</v>
+        <v>0.104226</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0195095</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.104226</v>
-      </c>
-      <c r="I3" t="n">
         <v>47.9</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1869,19 +1619,13 @@
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.11262</v>
+        <v>0.134507</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0218868</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.134507</v>
-      </c>
-      <c r="I4" t="n">
         <v>47</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1902,19 +1646,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0783596</v>
+        <v>0.0980468</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0196872</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0980468</v>
-      </c>
-      <c r="I5" t="n">
         <v>48</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1935,19 +1673,13 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0755546</v>
+        <v>0.094898</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0193434</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.094898</v>
-      </c>
-      <c r="I6" t="n">
         <v>48.4</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1968,19 +1700,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0853757</v>
+        <v>0.106694</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0213178</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.106694</v>
-      </c>
-      <c r="I7" t="n">
         <v>46.7</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2001,19 +1727,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08836239999999999</v>
+        <v>0.108052</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0196897</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.108052</v>
-      </c>
-      <c r="I8" t="n">
         <v>46.6</v>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2034,19 +1754,13 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0764924</v>
+        <v>0.0953059</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0188136</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0953059</v>
-      </c>
-      <c r="I9" t="n">
         <v>48</v>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2067,19 +1781,13 @@
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0800889</v>
+        <v>0.099966</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0198771</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.099966</v>
-      </c>
-      <c r="I10" t="n">
         <v>46.8</v>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2100,19 +1808,13 @@
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0932211</v>
+        <v>0.115788</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0225669</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.115788</v>
-      </c>
-      <c r="I11" t="n">
         <v>47.9</v>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2135,19 +1837,13 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.08612110000000002</v>
+        <v>0.10642467</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02030357</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0.10642467</v>
-      </c>
-      <c r="I12" t="n">
         <v>47.42</v>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
